--- a/AAII_Financials/Quarterly/AKZOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKZOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="92">
   <si>
     <t>AKZOY</t>
   </si>
@@ -656,177 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -869,86 +873,89 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3">
         <v>2886400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3093000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3104300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2739600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2605100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2595300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2656600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2310100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2203300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2362300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2167600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2323700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2617300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2937500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2883400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2584600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2730100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2576300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2685700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2389200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2561500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2714100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2842000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2790100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>11073700</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4225700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,86 +998,89 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>1855200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2036000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1980300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1675200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1566500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1597000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1562700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1291300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1230800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1306700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1210900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1289400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1489600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1688000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1617600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1504600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1605200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1468700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1526200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1379100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1458600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1539400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1574200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1529500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>5984100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2420400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1113,86 +1123,89 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>1031200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1056900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1124000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1064400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1038600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>998300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1094000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1018800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>972500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1055500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>956700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1034300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1127700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1249500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1265800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1080000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1124900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1107600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1159500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1010200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1102900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1174700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1267800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1260700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>5089600</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1805300</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1526,8 +1546,8 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1560,23 +1580,23 @@
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>4700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>3500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>4700</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
@@ -1584,25 +1604,28 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>4500</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>10100</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>29200</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
       <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
         <v>14100</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>-14100</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1645,8 +1668,8 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,8 +1790,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1808,86 +1835,89 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>2772300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2911400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2881300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2487900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2382900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2351900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2250400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2000800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1960900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2023900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1941800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2112500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2415400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2635000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2521000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2451000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2649700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2313800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2474900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2270700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2405500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2472900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2546900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2546000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>9990300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3692800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1930,86 +1960,89 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>114100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>181600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>223100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>251700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>222200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>243400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>406300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>309300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>242400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>338400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>225800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>211100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>202000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>302600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>362300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>133700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>80400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>262500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>210800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>118600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>156000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>241200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>295100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>244200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1083400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>532900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,86 +2130,89 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>-18800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>13000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>17300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>7500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>23300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>16300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>8000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>8300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>10200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4700</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>8200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>10600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>8300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>8900</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>49400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>11200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-5600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>14600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>12900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>25800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2218,86 +2255,89 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>200500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>285300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>324300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>361300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>341500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>344600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>519500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>412400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>340100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>441100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>320700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>322900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>322200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>409100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>475300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>244900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>158500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>337800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>276700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>233900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>236700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>313000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>390500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>342800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1820600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>713700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,86 +2380,89 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>38800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>28100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>31600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>17400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>20600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>17400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>17000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>17600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>18500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>21000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>23500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>20100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>28400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>26600</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>24200</v>
       </c>
       <c r="AJ22" s="3">
         <v>24200</v>
       </c>
       <c r="AK22" s="3">
-        <v>25800</v>
+        <v>24200</v>
       </c>
       <c r="AL22" s="3">
         <v>25800</v>
       </c>
       <c r="AM22" s="3">
+        <v>25800</v>
+      </c>
+      <c r="AN22" s="3">
         <v>24700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>25800</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>111500</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2462,86 +2505,89 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>56500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>152400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>198000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>247400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>219000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>229400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>410500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>308300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>233400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>329000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>204000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>204400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>185600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>276800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>347000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>124200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>60300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>244800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>186700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>143800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>141400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>209800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>285000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>231200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>997700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>505900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2584,86 +2630,89 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>37700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>55100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>72900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>67300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>51700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>130100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>74500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>51900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>85100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>57800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>61000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>92200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>62500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>81200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>36700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>7100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>73100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>51600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-1100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>90900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>64000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>70700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>61000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>274700</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>153800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,8 +2833,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2828,86 +2880,89 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>18800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>97300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>125100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>180100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>216800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>177700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>280400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>233800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>181500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>243900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>146200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>143400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>93400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>214400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>265900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>87500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>53200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>171700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>135100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>144900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>50500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>145900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>214300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>170200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>723100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>352100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2950,86 +3005,89 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>8900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>95100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>121900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>167100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>201600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>176600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>268700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>223600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>167600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>233500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>140700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>129800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>87600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>198400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>252900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>76900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>41400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>163900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>116400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>121900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>31400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>135800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>187400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>145600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>626800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>334500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3194,86 +3255,89 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-4300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-6500</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>1100</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>7400</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>7000</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>18800</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>6877400</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>169500</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>181200</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>155900</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>52700</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>108800</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>150300</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>136200</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>511800</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,86 +3630,89 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>18800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-13000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-17300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-7500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-23300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-10600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-8300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-8900</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-49400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-11200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>5600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-12900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-25800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3682,86 +3755,89 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>8900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>90800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>115300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>167100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>202700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>176600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>276100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>221500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>166600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>228300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>140700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>128700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>94600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>198400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>271700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>76900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6918800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>333400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>297600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>277800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>84100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>244600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>337700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>281700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1138600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>334500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,8 +3958,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3926,213 +4005,219 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>8900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>90800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>115300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>167100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>202700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>176600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>276100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>221500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>166600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>228300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>140700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>128700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>94600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>198400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>271700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>76900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6918800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>333400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>297600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>277800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>84100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>244600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>337700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>281700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1138600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>334500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,226 +4305,230 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3647900</v>
+      </c>
+      <c r="E41" s="3">
         <v>3185700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1899700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1551100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1822700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1728300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1348000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2183800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1249300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1153300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1672400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1765500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1635400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1312500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1606000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1454600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1170800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1538500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1248900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1170600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1286500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1221900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1601800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1558900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1341800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>939400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1483800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>765600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1362300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1578000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3310900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1151900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1051900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1258300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1483300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1218500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1169100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1488400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1736100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1974300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>310800</v>
+      </c>
+      <c r="E42" s="3">
         <v>311300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>354600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>16400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>187000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>170800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>247600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>31300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>292900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>248700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>256600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>348800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>372200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>24900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>850900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1172900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>62900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>14000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>312100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>307300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>249400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>114200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>54500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>161100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1930600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1795200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3195000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>6458600</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4454,8 +4544,8 @@
       <c r="AM42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN42" s="3">
-        <v>0</v>
+      <c r="AN42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO42" s="3">
         <v>0</v>
@@ -4463,862 +4553,886 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3314300</v>
+      </c>
+      <c r="E43" s="3">
         <v>3267600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3006900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3327500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3311800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3217700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2681400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3341500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3271200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3185900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2834100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3170000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3215100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3019300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2896400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3261600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3159800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2813400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2535700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2563000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2651300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2351900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1988800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2312400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2390200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2540500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2490100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2944900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2930400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2846100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2532600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2519800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2661600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2446300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2203600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3470300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3574700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3716300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3271400</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3458000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1944500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1855200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1795200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1842100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1923700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1920700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1781800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2013200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1967200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1919300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1822700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1817300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1918100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1998000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2041300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2220800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2304600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2009400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1788800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1684300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1481200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1330100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1156000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1177000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1285100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1366200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1329700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1495700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1441100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1450200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1347300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1273700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1286900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1279200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1227500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1826600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1827700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1923900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1798300</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1840500</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E45" s="3">
         <v>58800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>366100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>361700</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>16600</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>15500</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
         <v>164300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>159500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>161500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>106600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>74100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>65300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>54900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>69500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>76400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>73400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>73500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>89400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>94100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>95800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>87500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5620000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5451600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>5298900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>5231800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>75200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>61700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>77500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>69300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>63400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9278000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8678700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7116400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7089100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7436300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7053600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6042000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7786100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6490900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6289800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6680700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7001500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7025100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6678600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6915900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6961900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7650400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7693700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5797800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5538500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5805200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5276500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5050800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5232100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5148000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4921700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5538200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7226200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7623100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9165100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13737000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>10565400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>10451900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>10282800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>10146200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6590600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6633200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>7206000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>6875000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>7336300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>269600</v>
+      </c>
+      <c r="E47" s="3">
         <v>277900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>272400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>269900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>291300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>252900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>236000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>252100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>250700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>240600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>238800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>223300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>216200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>218400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>213800</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V47" s="3">
         <v>193000</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z47" s="3">
         <v>165600</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD47" s="3">
         <v>175100</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AF47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG47" s="3">
         <v>3098000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2324400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2293800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2390300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2310200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1479900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1880500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1952300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2290100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>844000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>2155100</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2704200</v>
+      </c>
+      <c r="E48" s="3">
         <v>2693400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2739200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2666900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2671800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2622100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2526100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2600900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2499700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2507300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2537900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2387800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2457400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2430500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2502100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2457500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2454800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2276300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2280900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2178600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2135000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2066100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1939900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1986500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2158900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2258200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2421200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2497800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2412800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2539700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2067700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1880700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1888600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1903900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2055500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4525000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>4558600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>4927700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>4918300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>4683500</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4409900</v>
+      </c>
+      <c r="E49" s="3">
         <v>4421800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4459300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4440900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4451000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4313700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4191900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4472500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4346900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4425500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4510900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4393500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4409400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4395900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4510100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4624300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4675600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4032900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4000300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3925300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3838400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3703500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3544800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3656500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3897800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4024100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4231900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4168600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3996200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4077500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4090500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3714900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3720000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3711200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3824900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4703400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>4747100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5146000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5180000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>4658900</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,98 +5678,101 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1769700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1783700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1256300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1838600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1791000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1808300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1224800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2006500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1930800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1974300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1457900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1909400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2119000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2211000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2185300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2747100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2830100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2978300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2773100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2849500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2925400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2626500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2441600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2875000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3204000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3667300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2791300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3312400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2946900</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5665,26 +5785,29 @@
       <c r="AJ52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL52" s="3">
         <v>645100</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AO52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP52" s="3">
         <v>1193800</v>
       </c>
-      <c r="AP52" s="3" t="s">
+      <c r="AQ52" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18431400</v>
+      </c>
+      <c r="E54" s="3">
         <v>17855400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16381400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16305300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16641200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16050600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14752000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17118000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15519100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15437500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16091500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15915500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16227100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15934400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16327100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16790800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17610900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16981300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15045100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14491800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14704100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13672600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13142700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13750100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>14408700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>14871400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15157700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17205000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16979000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>18880300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>22219600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>18454800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>18450800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>18208100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>18151600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>17699400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>17891300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>19569800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>19011000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>18833800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2779600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2587300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2532600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2489700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2528500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2496800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2298400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2615400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2598300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2514800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2555500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2478800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2492400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2356600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3102400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3421500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3582000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3349400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3195900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3207000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3038600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2791900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2573300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2514800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2521100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2620600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2808800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3006100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2999800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3069600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3128800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2872000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2939300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2889900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3134800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3987600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3949400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>4215200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>4079000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3961600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1247600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1560000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1399600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1988700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2571900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1855800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1756900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2874200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2400100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2099500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2650600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2478800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2624500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2683600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2816600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2110600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2523300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2178700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1686900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1166300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>642200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>143900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>118700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>173300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>200700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>333100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>197300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>857500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>834100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>839900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>708600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1598300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1698600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1585500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1091700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>151500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>344500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>495300</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>102100</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>191300</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>896800</v>
+      </c>
+      <c r="E59" s="3">
         <v>910900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>369800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1197900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>964200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>827900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>316800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>962500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>901100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>992600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>439900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1097600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1089500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1015900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>445300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>487400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>441800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>406900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>395700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>372600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>392500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>362400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>393000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>423500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>435300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>444900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>498500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>539000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>509400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>508600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>515700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2787800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2813100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2820800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2866700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>570000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>658600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>743000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>764200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>825200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4924000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5058200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4939500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5676400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6064600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5180500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4897000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6452200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5899500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5606900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6307100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6055200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6206300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6056100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6364300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6019500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6547100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5935000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5278500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4745900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4073300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3298200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3085000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3111600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3157100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3398600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3504600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4402600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4343300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4418100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4353100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7258100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7451000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7296200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7093200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4709000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4952500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5453500</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4945300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4978100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6283600</v>
+      </c>
+      <c r="E61" s="3">
         <v>5484800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4309000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4290700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4293600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4507100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3800600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4095500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3409400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3434000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3498400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3878100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4019700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3611500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3690500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3633300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3703900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3448100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2161700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2153800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2921100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2822500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2763800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2865600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3031600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2298800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2383900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2496500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2397500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2442700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2128000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2544200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2524300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2523200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2580600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2964300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2967700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3107100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3103600</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3096500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>880800</v>
+      </c>
+      <c r="E62" s="3">
         <v>910900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>547100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>935100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>606000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>566400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>165600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>633500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>612900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>648400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>178000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>556700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>603700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>606300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1235000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1361700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1447200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1455000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1495000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1426900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1441000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1320900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1359500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1492500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1614500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1619100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1601700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1707600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1559900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1580400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1498700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1280400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1300000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1349400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1401400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2330400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2374100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2616400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2705600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>2730300</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12681400</v>
+      </c>
+      <c r="E66" s="3">
         <v>12028100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10719700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11442000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11491500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10795500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9766000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11754400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10472500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10249200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11066700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11032000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11403900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10889800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11527900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11254400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11948400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11070300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9163900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8559200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8665000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7661100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7411700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7681500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8030200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7558200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7744600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>8886100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8557100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8694300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>8221200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>11554500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>11777100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>11663000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>11571100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>10518700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>10832800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>11756900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>11319000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>11393000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6119000</v>
+      </c>
+      <c r="E72" s="3">
         <v>6320800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1022700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5631800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5879000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5610700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>813700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5783000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5374500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5513000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>750500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5235000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5269700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5503000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5467100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5809800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5974800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6299500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6337600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6532500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6652700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6591300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6507000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6885400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7111600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7988400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>7843800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>8826100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>8991200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>10589300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12978800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5989900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5698600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5812800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5750200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>6329100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5928600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>6400800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>6276400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>6298700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5544400</v>
+      </c>
+      <c r="E76" s="3">
         <v>5627800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5470200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4612200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4899600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4997800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4735500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5104800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4789500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4936900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4777300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4647500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4577500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4801200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4799200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5536400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5662500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5911100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5881200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5932600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6039100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6011500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5731100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6068600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6378600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7313200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7413100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8318900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8421800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10186000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13998400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6900300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6673600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6545200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6580500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>7180700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>7058400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>7812900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7692000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>7440800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,135 +8688,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8670,86 +8865,89 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>8900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>90800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>115300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>167100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>202700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>176600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>276100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>221500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>166600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>228300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>140700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>128700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>94600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>198400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>271700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>76900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6918800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>333400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>297600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>277800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>84100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>244600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>337700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>281700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1138600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>334500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E83" s="3">
         <v>101600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>107100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>98600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>96000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>79600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>73000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>75300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>72800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>75900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>71600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>69000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>78900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>105200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>104800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>94700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>96600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>101900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>93700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>89900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>86800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>89800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>94400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>98200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>101600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>115600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>106600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>104700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>100500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>69800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>66500</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>65900</v>
       </c>
       <c r="AJ83" s="3">
         <v>65900</v>
       </c>
       <c r="AK83" s="3">
+        <v>65900</v>
+      </c>
+      <c r="AL83" s="3">
         <v>154800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>170500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>178400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>185500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>711300</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>178400</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>194200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-99200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>542400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>388400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>274800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-122100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>411000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>327900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>160700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-186600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>631100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>313300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>331900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-55400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>322300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>126400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-56600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-110700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>191900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>312300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>177700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-31600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>612400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>473300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>336000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-181800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>336200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>377300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>177600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-856400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>287400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>787500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>16500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-500700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>593500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>466700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>350100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-338100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1515400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>704300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-70800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-66900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-117400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-77400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-84600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-76700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-118000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-85900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-79300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-44200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-126000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-57200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-61100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-67400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-96000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-72000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-67000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-57000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-99000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-70000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-65600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-58200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-101700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-66400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-50200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-51900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-92200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-63700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-54100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-43800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-63900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-39500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-37300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-95400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-66200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-68400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-193700</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1488400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-150200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>486100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>138600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-68100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-35200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-314500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-37500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>236300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-123800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>45900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-75000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-465200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>757600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-342800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1151200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-139800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>235800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-57100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-173500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-267300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-121400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-157100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>115200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>637400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>841600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1430500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>3031800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>4023000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-365500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-12100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-239000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-362400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-71800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-44600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1149200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-133800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>307300</v>
+      </c>
+      <c r="E96" s="3">
         <v>3500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>43400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>31700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>315900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>6500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>53800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>5600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>292500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>8600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>60800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>16900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>292600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>4300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-99700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>80000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-387400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-7600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-97600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-10800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-304700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-81800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>1000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-310900</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-95700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-9800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-375300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1213700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-159700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-25500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-334900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-190000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1077100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-14600</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-235600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1200</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-394400</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-25800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>222800</v>
+      </c>
+      <c r="E100" s="3">
         <v>1403200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-708000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-621800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-374600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>509100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1035300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>919000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>78200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-626800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-610100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-140800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-26200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-128200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>363300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-624600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-16300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1525500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>33600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-707500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-114300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-245000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-220400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-36300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>325100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-446000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1092700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-923600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1804600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3968600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2222700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-268000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-225100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>241600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-77400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-97600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-325400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>11700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-238300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-124400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-48200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>7200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-23400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-16100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-70700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-17500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-16300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-52400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>9800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>16700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>10000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-54300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>10800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>17400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>9800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>14100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>6500</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>16300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-23900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-41800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>19600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-15300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>27200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>17700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-26600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-19100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-51600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>7000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>17600</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>502700</v>
+      </c>
+      <c r="E102" s="3">
         <v>1315600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>329900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-268700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>311300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-652200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>909000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>185400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-580400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-173500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>168300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>334100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-274900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>166100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>270200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-398200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>273400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>99700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-152900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>6300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-433800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>120700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>291600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>501800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-554400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>64200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>117600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-211800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1766100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2105600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>127400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-208600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-275600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>276000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>173900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-194100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-459000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>145600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>443700</v>
       </c>
     </row>
